--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_234_Faeroe_Isl_Denmark.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_234_Faeroe_Isl_Denmark.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra5ba5322cf864c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R04c16a637dfc4d8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R79ca2a3153504f05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re838b21f60504724"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rce2983bc6920427c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8ede7b00ef0d49d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R942c9113bf034b80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rabe7eef9a2794ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb24d23c5469a4f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R18d5d01b9a5f4e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9b535f09290e44e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9cae6bfd40b24213"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ234CommercialTable" displayName="EEZ234CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ234CommercialTable" displayName="EEZ234CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ234FunctionalTable" displayName="EEZ234FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ234FunctionalTable" displayName="EEZ234FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ234ValidationTable" displayName="EEZ234ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ234ValidationTable" displayName="EEZ234ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -7662,7 +7616,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de55295ae0f4d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R614adaa67afc4ac1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7672,20 +7626,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7693,606 +7637,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>366765.64756317995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.127527269795051</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1341.3041546220297</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>366765.64756317995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1351.673164858768</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$105,A2,'Species'!$U$2:$U$105))</x:f>
-        <x:v>495747283.6031989</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.127527269795051</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1341.3041546220297</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>491944286.84913236</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>3802996.754066527</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0077305435914796</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.007730543591479528</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>111.63080107409999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.7646484749593223</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>58.163224455978344</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>111.63080107409999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>64.45973785960857</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$105,A3,'Species'!$U$2:$U$105))</x:f>
-        <x:v>7195.692174294596</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.7646484749593223</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>58.163224455978344</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>6492.807339073546</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>702.8848352210498</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1082559205154767</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10825592051547674</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3088.9584391884996</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.059680524327518</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1147.3093273983566</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3088.9584391884996</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1761.7913865412943</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$105,A4,'Species'!$U$2:$U$105))</x:f>
-        <x:v>5442100.371546339</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.059680524327518</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1147.3093273983566</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3543990.8292268347</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1898109.5423195045</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.5355853425652348</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.5355853425652347</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>97850.11044760559</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3799374696161055</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>239.8487556249567</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>97850.11044760559</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>239.8561937021472</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$105,A5,'Species'!$U$2:$U$105))</x:f>
-        <x:v>23469955.045297384</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3799374696161055</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>239.8487556249567</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>23469227.228622776</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>727.8166746087372</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0000310115312925</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00003101153129239386</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5554.1009274917</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0023850219873687</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.05506823189301</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5554.1009274917</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.193386792313394</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$105,A6,'Species'!$U$2:$U$105))</x:f>
-        <x:v>56615.09903746947</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0023850219873687</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.05506823189301</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>55846.86379274929</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>768.2352447201774</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0137561036116753</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.013756103611675306</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>26988.684557198296</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3975901420975263</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>249.79868171189685</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>26988.684557198296</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>451.8696426841936</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$105,A7,'Species'!$U$2:$U$105))</x:f>
-        <x:v>12195367.247377608</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3975901420975263</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>249.79868171189685</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6741737.823526363</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>5453629.423851245</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.8089352577342803</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.8089352577342804</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>51928.590562487094</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.639241140981387</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>435.75375776742356</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>51928.590562487094</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>454.7229121841949</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$105,A8,'Species'!$U$2:$U$105))</x:f>
-        <x:v>23613119.92619483</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.639241140981387</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>435.75375776742356</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>22628078.473169718</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>985041.4530251138</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.043531820618047</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.043531820618046946</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>18787.2447141812</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.349984490600484</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>223.86411914310392</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>18787.2447141812</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>223.86516418346469</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$105,A9,'Species'!$U$2:$U$105))</x:f>
-        <x:v>4205809.622495104</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.349984490600484</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>223.86411914310392</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>4205789.98906611</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>19.63342899363488</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.000004668190529</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.000004668190528931868</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1963.8113129739</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7645933194303547</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>581.5583817813311</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1963.8113129739</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>586.192061674837</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$105,A10,'Species'!$U$2:$U$105))</x:f>
-        <x:v>1151170.6022925389</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7645933194303547</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>581.5583817813311</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1142070.9292969725</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>9099.67299556639</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0079676951423393</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.007967695142339276</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>287.21538161899997</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.914567678484992</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>821.4245499424019</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>287.21538161899997</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1047.5666390699862</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$105,A11,'Species'!$U$2:$U$105))</x:f>
-        <x:v>300877.2520118193</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.914567678484992</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>821.4245499424019</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>235925.76558292226</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>64951.48642889701</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2753047606666263</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.2753047606666264</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0045f86dd89a468b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccb46a118e224ebe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8302,20 +7852,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8323,1254 +7863,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>92.0823955691</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.9795094378812825</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>953.9144726322712</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>92.0823955691</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>954.470124545787</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$105,A2,'Species'!$U$2:$U$105))</x:f>
-        <x:v>87889.8955673133</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.9795094378812825</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>953.9144726322712</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>87838.72980801422</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>51.1657592990814</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000582496575382</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0005824965753820947</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2622.1929192933</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.448004056816334</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2805.4598440921022</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2622.1929192933</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2806.813211224822</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$105,A3,'Species'!$U$2:$U$105))</x:f>
-        <x:v>7360005.728252618</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.448004056816334</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2805.4598440921022</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>7356456.938539996</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3548.7897126218304</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0004824047421566</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0004824047421565066</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>47.3148323582</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.544311544389624</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>350.1962928698193</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>47.3148323582</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>355.06098471372496</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$105,A4,'Species'!$U$2:$U$105))</x:f>
-        <x:v>16799.65096866731</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.544311544389624</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>350.1962928698193</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>16569.47888959861</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>230.17207906869953</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.013891328786036</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.013891328786036154</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>39256.068657656506</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.095428244584507</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1245.7423950327689</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>39256.068657656506</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1255.0656396522963</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$105,A5,'Species'!$U$2:$U$105))</x:f>
-        <x:v>49268942.92005613</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.095428244584507</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1245.7423950327689</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>48902948.98915983</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>365993.9308962971</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0074840871248363</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.007484087124836293</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>9357.069111680601</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.2985790433190925</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1988.7447368936591</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>9357.069111680601</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2206.3861669099642</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$105,A6,'Species'!$U$2:$U$105))</x:f>
-        <x:v>20645307.850832585</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.2985790433190925</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1988.7447368936591</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>18608821.948605023</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2036485.902227562</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1094365837801046</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.10943658378010454</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>410.27239468339997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.2996583499429732</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>199.36933025812974</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>410.27239468339997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>226.4274202440575</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$105,A7,'Species'!$U$2:$U$105))</x:f>
-        <x:v>92896.91992551403</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.2996583499429732</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>199.36933025812974</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>81795.73255142852</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>11101.187374085508</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1357184174260646</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1357184174260645</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>73.1691900002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.643681649338926</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>440.23204213441477</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>73.1691900002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>476.6723993762394</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$105,A8,'Species'!$U$2:$U$105))</x:f>
-        <x:v>34877.73335781128</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.643681649338926</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>440.23204213441477</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>32211.421935109047</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2666.3114227022343</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0827753406252478</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08277534062524794</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1573.8520598225</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.79</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>616.5950018614822</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1573.8520598225</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$105,A9,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>970429.3137559519</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.79</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
-        <x:v>970429.3137559519</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>91.9043916188</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.300406844409167</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1997.1323402553649</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>91.9043916188</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2073.2577953843806</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$105,A10,'Species'!$U$2:$U$105))</x:f>
-        <x:v>190541.49635373603</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.300406844409167</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1997.1323402553649</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>183545.2327133996</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>6996.26364033643</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0381173814046203</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.03811738140462023</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>55.5836742308</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.7312980469834796</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>53.86393123030686</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>55.5836742308</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>57.85694809352014</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$105,A11,'Species'!$U$2:$U$105))</x:f>
-        <x:v>3215.9017548185284</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.7312980469834796</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>53.86393123030686</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>2993.955206295591</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>221.94654852293752</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0741315528222453</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.07413155282224516</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>18861.090097317297</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.3540805933109175</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>225.98550993033237</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>18861.090097317297</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>233.517702770094</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$105,A12,'Species'!$U$2:$U$105))</x:f>
-        <x:v>4404398.431265304</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.3540805933109175</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>225.98550993033237</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4262333.063484192</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>142065.36778111197</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0333304238934773</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.03333042389347734</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>362.4317074741</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.651155877299256</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>447.8740266108966</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>362.4317074741</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>448.0204536319997</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$105,A13,'Species'!$U$2:$U$105))</x:f>
-        <x:v>162376.8179931665</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.651155877299256</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>447.8740266108966</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>162323.74819788773</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>53.06979527877411</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.00032693796113</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0003269379611298594</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>308780.00115113065</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>4.130013204140717</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>1349.0038966207092</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>308780.00115113065</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>1349.6508762407955</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$105,A14,'Species'!$U$2:$U$105))</x:f>
-        <x:v>416745199.11925733</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>4.130013204140717</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>1349.0038966207092</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>416545424.7514223</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>199774.36783504486</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0004795980365269</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.00047959803652689796</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>34154.708044732</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.499072218696306</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>315.55293117505204</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>34154.708044732</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>447.2489049668337</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$105,A15,'Species'!$U$2:$U$105))</x:f>
-        <x:v>15275655.772468291</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.499072218696306</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>315.55293117505204</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>10777618.236943312</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>4498037.535524979</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.4173498667921538</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.41734986679215386</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>149063.72355246454</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.4662780239248407</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>292.60249427410145</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>149063.72355246454</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>304.7660907591484</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$105,A16,'Species'!$U$2:$U$105))</x:f>
-        <x:v>45429568.30108702</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.4662780239248407</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>292.60249427410145</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>43616417.317236245</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1813150.9838507771</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0415703786641426</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.04157037866414259</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>0.0019222656</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>0.0019222656</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$105,A17,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>0.3046585663542179</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
-        <x:v>0.3046585663542179</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>5554.1009274917</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.0023850219873687</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.05506823189301</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>5554.1009274917</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.193386792313394</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$105,A18,'Species'!$U$2:$U$105))</x:f>
-        <x:v>56615.09903746947</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.0023850219873687</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.05506823189301</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>55846.86379274929</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>768.2352447201774</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0137561036116753</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.013756103611675306</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>56.047126843300006</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.7977231288885007</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>62.76580870958328</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>56.047126843300006</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>71.00792928427909</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$105,A19,'Species'!$U$2:$U$105))</x:f>
-        <x:v>3979.7904194760667</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.7977231288885007</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>62.76580870958328</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>3517.8432421683187</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>461.947177307748</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1313154525393276</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.13131545253932755</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>113.545735195</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.1524493954552173</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>142.05266816427562</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>113.545735195</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>142.05966009360193</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$105,A20,'Species'!$U$2:$U$105))</x:f>
-        <x:v>16130.268546879834</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.1524493954552173</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>142.05266816427562</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>16129.474643124047</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0.7939037557862321</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.00004922068284</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.00004922068284007447</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>0.006970666699999999</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.38</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>239.88329190194898</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>0.006970666699999999</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$105,A21,'Species'!$U$2:$U$105))</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1.6721464747472952</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.38</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
-        <x:v>1.6721464747472952</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>2678.6860445050993</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>4.176086893837254</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>1499.9849231454527</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>2678.6860445050993</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>1996.9505058623313</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$105,A22,'Species'!$U$2:$U$105))</x:f>
-        <x:v>5349203.451620826</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>4.176086893837254</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>1499.9849231454527</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>4017988.680597778</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1331214.7710230476</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.3313137185904156</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.33131371859041564</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>122.1418</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.7865214038109802</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>611.675948108024</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>122.1418</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>617.7903248541618</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$105,A23,'Species'!$U$2:$U$105))</x:f>
-        <x:v>75458.02230027206</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.7865214038109802</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>611.675948108024</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>74711.20131862066</x:v>
       </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>746.820981651399</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.009996104579639</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.00999610457963905</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3d7b3d99a774ec0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra948358248554e32"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9745,7 +8471,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9844,7 +8570,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>566189494.4616263</x:v>
+        <x:v>553973447.5587559</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9858,7 +8584,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>566189494.4616263</x:v>
+        <x:v>555775924.898848</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9872,7 +8598,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-12216046.902870297</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9886,7 +8612,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>1.1920928955078125e-7</x:v>
+        <x:v>-10413569.562778115</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9897,9 +8623,9 @@
         <x:v>EEZ_234</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9911,47 +8637,19 @@
         <x:v>EEZ_234</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_234</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_234</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a624fa9075e45e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f64b51c7e7c42e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9998,7 +8696,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
